--- a/artfynd/S 649-2023 artfynd.xlsx
+++ b/artfynd/S 649-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134736762</v>
+        <v>134608641</v>
       </c>
       <c r="B7" t="n">
-        <v>56706</v>
+        <v>57776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206046</v>
+        <v>102118</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1270,21 +1270,25 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog V Lilla Björka, Dädesjö, Sm</t>
+          <t>Kviudda, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507847</v>
+        <v>507739</v>
       </c>
       <c r="R7" t="n">
-        <v>6316454</v>
+        <v>6316115</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,12 +1312,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>23:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>23:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,19 +1342,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Johannes Rydström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Johannes Rydström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134608641</v>
+        <v>134735543</v>
       </c>
       <c r="B8" t="n">
         <v>57776</v>
@@ -1383,17 +1397,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kviudda, Sm</t>
+          <t>Kviudda, Dädesjö, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507739</v>
+        <v>507703</v>
       </c>
       <c r="R8" t="n">
-        <v>6316115</v>
+        <v>6316034</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1431,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:49</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:49</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,72 +1461,76 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johannes Rydström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johannes Rydström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134735543</v>
+        <v>134608642</v>
       </c>
       <c r="B9" t="n">
-        <v>57776</v>
+        <v>57824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102118</v>
+        <v>102975</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kviudda, Dädesjö, Sm</t>
+          <t>Kviudda, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507703</v>
+        <v>507739</v>
       </c>
       <c r="R9" t="n">
-        <v>6316034</v>
+        <v>6316115</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,22 +1554,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,76 +1584,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Johannes Rydström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Johannes Rydström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134608642</v>
+        <v>127902690</v>
       </c>
       <c r="B10" t="n">
-        <v>57824</v>
+        <v>56845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102975</v>
+        <v>100053</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kviudda, Sm</t>
+          <t>Växjö kommun, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507739</v>
+        <v>507646</v>
       </c>
       <c r="R10" t="n">
-        <v>6316115</v>
+        <v>6315945</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,22 +1670,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:49</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:49</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,76 +1700,79 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johannes Rydström</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johannes Rydström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134735544</v>
+        <v>66343246</v>
       </c>
       <c r="B11" t="n">
-        <v>57824</v>
+        <v>107908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102975</v>
+        <v>219955</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>pulli</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kviudda, Dädesjö, Sm</t>
+          <t>Dädesjö-Linnebjörke 900 m SO, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507703</v>
+        <v>509099</v>
       </c>
       <c r="R11" t="n">
-        <v>6316034</v>
+        <v>6316090</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1782,27 +1796,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>22:50</t>
+          <t>2017-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>22:50</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tiggande, i nordost</t>
+          <t>2017-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,48 +1812,53 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Lisa Petersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Lisa Petersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127902690</v>
+        <v>108731310</v>
       </c>
       <c r="B12" t="n">
-        <v>56845</v>
+        <v>57794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100053</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1862,24 +1866,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Växjö kommun, Sm</t>
+          <t>Sågaretorpet, Sågaretorpet, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507646</v>
+        <v>508548</v>
       </c>
       <c r="R12" t="n">
-        <v>6315945</v>
+        <v>6312964</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,22 +1910,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>04:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>04:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,79 +1940,72 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66343246</v>
+        <v>78730798</v>
       </c>
       <c r="B13" t="n">
-        <v>107908</v>
+        <v>58497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219955</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dädesjö-Linnebjörke 900 m SO, Sm</t>
+          <t>Sågaretorpet-Segskinnet, Sågaretorpet, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509099</v>
+        <v>508521</v>
       </c>
       <c r="R13" t="n">
-        <v>6316090</v>
+        <v>6312746</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-06-20</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-06-20</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,31 +2045,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Petersson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Petersson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108731310</v>
+        <v>78730793</v>
       </c>
       <c r="B14" t="n">
-        <v>57794</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,49 +2072,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sågaretorpet, Sågaretorpet, Sm</t>
+          <t>Sågaretorpet-Segskinnet, Sågaretorpet, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508548</v>
+        <v>508521</v>
       </c>
       <c r="R14" t="n">
-        <v>6312964</v>
+        <v>6312746</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2143,22 +2130,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>04:10</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>04:10</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>78730798</v>
+        <v>78730754</v>
       </c>
       <c r="B15" t="n">
-        <v>58497</v>
+        <v>43219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,35 +2173,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102990</v>
+        <v>201028</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2276,6 +2254,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2294,36 +2273,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>78730793</v>
+        <v>78730767</v>
       </c>
       <c r="B16" t="n">
-        <v>58114</v>
+        <v>43378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>201075</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2377,6 +2365,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2395,47 +2384,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>78730754</v>
+        <v>116144793</v>
       </c>
       <c r="B17" t="n">
-        <v>43219</v>
+        <v>104628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>201028</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2473,12 +2465,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,61 +2498,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>78730767</v>
+        <v>7508</v>
       </c>
       <c r="B18" t="n">
-        <v>43378</v>
+        <v>56766</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>201075</v>
+        <v>100077</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sågaretorpet-Segskinnet, Sågaretorpet, Sm</t>
+          <t>Ossmaden, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508521</v>
+        <v>509194</v>
       </c>
       <c r="R18" t="n">
-        <v>6312746</v>
+        <v>6312808</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2584,12 +2563,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2009-03-31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2009-03-31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,51 +2577,50 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Mia Bisther</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Mia Bisther</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116144793</v>
+        <v>82515894</v>
       </c>
       <c r="B19" t="n">
-        <v>104628</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2650,28 +2628,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sågaretorpet-Segskinnet, Sågaretorpet, Sm</t>
+          <t>Osmaden, Sågaretorpet, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508521</v>
+        <v>509218</v>
       </c>
       <c r="R19" t="n">
-        <v>6312746</v>
+        <v>6312793</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2698,12 +2672,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2020-02-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2020-02-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,7 +2686,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,55 +2697,66 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Tomas Lundqvist, Johannes Rydström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7508</v>
+        <v>104510627</v>
       </c>
       <c r="B20" t="n">
-        <v>56766</v>
+        <v>93235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100077</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ossmaden, Sm</t>
+          <t>Kvarnvägen, Kvarnvägen, Kattafly, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509194</v>
+        <v>508240</v>
       </c>
       <c r="R20" t="n">
-        <v>6312808</v>
+        <v>6311562</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,12 +2780,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2009-03-31</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2009-03-31</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,25 +2794,26 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mia Bisther</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mia Bisther</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>82515894</v>
+        <v>122666650</v>
       </c>
       <c r="B21" t="n">
         <v>58114</v>
@@ -2858,7 +2843,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2871,14 +2856,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Osmaden, Sågaretorpet, Sm</t>
+          <t>Kvarnvägen, Kvarnvägen, Kattafly, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509218</v>
+        <v>508240</v>
       </c>
       <c r="R21" t="n">
-        <v>6312793</v>
+        <v>6311562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,12 +2890,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-02-29</t>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-02-29</t>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,66 +2925,63 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist, Johannes Rydström</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104510627</v>
+        <v>73290312</v>
       </c>
       <c r="B22" t="n">
-        <v>93235</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnvägen, Kvarnvägen, Kattafly, Sm</t>
+          <t>Linje 3, Herråkra 05F2C (Standardrutt), Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508240</v>
+        <v>510530</v>
       </c>
       <c r="R22" t="n">
-        <v>6311562</v>
+        <v>6310941</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3013,12 +3005,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
+          <t>2018-05-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
+          <t>2018-05-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,79 +3029,74 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122666650</v>
+        <v>73290284</v>
       </c>
       <c r="B23" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnvägen, Kvarnvägen, Kattafly, Sm</t>
+          <t>Linje 3, Herråkra 05F2C (Standardrutt), Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508240</v>
+        <v>510530</v>
       </c>
       <c r="R23" t="n">
-        <v>6311562</v>
+        <v>6310941</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3123,22 +3120,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,22 +3150,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>73290312</v>
+        <v>73290329</v>
       </c>
       <c r="B24" t="n">
-        <v>58327</v>
+        <v>58636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3176,16 +3173,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3195,7 +3192,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -3280,10 +3277,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>73290284</v>
+        <v>73290331</v>
       </c>
       <c r="B25" t="n">
-        <v>58439</v>
+        <v>58085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,26 +3288,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103018</v>
+        <v>205976</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3395,10 +3392,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>73290329</v>
+        <v>124350795</v>
       </c>
       <c r="B26" t="n">
-        <v>58636</v>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,45 +3403,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Linje 3, Herråkra 05F2C (Standardrutt), Sm</t>
+          <t>Magersryd, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510530</v>
+        <v>507952</v>
       </c>
       <c r="R26" t="n">
-        <v>6310941</v>
+        <v>6310311</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3468,22 +3466,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,39 +3496,39 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Ellen Flygare</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Ellen Flygare</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>73290331</v>
+        <v>100448862</v>
       </c>
       <c r="B27" t="n">
-        <v>58085</v>
+        <v>56522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205976</v>
+        <v>206004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3540,23 +3538,31 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Linje 3, Herråkra 05F2C (Standardrutt), Sm</t>
+          <t>Vägen Herråkra - Attsjö, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510530</v>
+        <v>507993</v>
       </c>
       <c r="R27" t="n">
-        <v>6310941</v>
+        <v>6310259</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3583,22 +3589,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,254 +3619,15 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Love Eriksen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Love Eriksen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>124350795</v>
-      </c>
-      <c r="B28" t="n">
-        <v>57141</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Magersryd, Sm</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>507952</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6310311</v>
-      </c>
-      <c r="S28" t="n">
-        <v>20</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Växjö</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Dädesjö</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Ellen Flygare</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Ellen Flygare</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>100448862</v>
-      </c>
-      <c r="B29" t="n">
-        <v>56522</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>206004</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Skogshare</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Lepus timidus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Vägen Herråkra - Attsjö, Sm</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>507993</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6310259</v>
-      </c>
-      <c r="S29" t="n">
-        <v>25</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Växjö</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Dädesjö</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Love Eriksen</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Love Eriksen</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 649-2023 artfynd.xlsx
+++ b/artfynd/S 649-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134608641</v>
+        <v>134736762</v>
       </c>
       <c r="B7" t="n">
-        <v>57776</v>
+        <v>56706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102118</v>
+        <v>206046</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1270,25 +1270,21 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kviudda, Sm</t>
+          <t>Skog V Lilla Björka, Dädesjö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507739</v>
+        <v>507847</v>
       </c>
       <c r="R7" t="n">
-        <v>6316115</v>
+        <v>6316454</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,22 +1308,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>23:49</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>23:49</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,19 +1328,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johannes Rydström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johannes Rydström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134735543</v>
+        <v>134608641</v>
       </c>
       <c r="B8" t="n">
         <v>57776</v>
@@ -1397,17 +1383,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kviudda, Dädesjö, Sm</t>
+          <t>Kviudda, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507703</v>
+        <v>507739</v>
       </c>
       <c r="R8" t="n">
-        <v>6316034</v>
+        <v>6316115</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,22 +1417,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,76 +1447,72 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Johannes Rydström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Johannes Rydström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134608642</v>
+        <v>134735543</v>
       </c>
       <c r="B9" t="n">
-        <v>57824</v>
+        <v>57776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102975</v>
+        <v>102118</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kviudda, Sm</t>
+          <t>Kviudda, Dädesjö, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507739</v>
+        <v>507703</v>
       </c>
       <c r="R9" t="n">
-        <v>6316115</v>
+        <v>6316034</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,22 +1536,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:49</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:49</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,69 +1566,76 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johannes Rydström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johannes Rydström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127902690</v>
+        <v>134608642</v>
       </c>
       <c r="B10" t="n">
-        <v>56845</v>
+        <v>57824</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100053</v>
+        <v>102975</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Växjö kommun, Sm</t>
+          <t>Kviudda, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507646</v>
+        <v>507739</v>
       </c>
       <c r="R10" t="n">
-        <v>6315945</v>
+        <v>6316115</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,22 +1659,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>23:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>23:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,79 +1689,76 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Johannes Rydström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Johannes Rydström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66343246</v>
+        <v>134735544</v>
       </c>
       <c r="B11" t="n">
-        <v>107908</v>
+        <v>57824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219955</v>
+        <v>102975</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>pulli</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dädesjö-Linnebjörke 900 m SO, Sm</t>
+          <t>Kviudda, Dädesjö, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509099</v>
+        <v>507703</v>
       </c>
       <c r="R11" t="n">
-        <v>6316090</v>
+        <v>6316034</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,12 +1782,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-06-20</t>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-06-20</t>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tiggande, i nordost</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,53 +1813,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Petersson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Petersson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108731310</v>
+        <v>127902690</v>
       </c>
       <c r="B12" t="n">
-        <v>57794</v>
+        <v>56845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>100053</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1866,27 +1862,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sågaretorpet, Sågaretorpet, Sm</t>
+          <t>Växjö kommun, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508548</v>
+        <v>507646</v>
       </c>
       <c r="R12" t="n">
-        <v>6312964</v>
+        <v>6315945</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,22 +1903,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>04:10</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>04:10</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,72 +1933,79 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>78730798</v>
+        <v>66343246</v>
       </c>
       <c r="B13" t="n">
-        <v>58497</v>
+        <v>107908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102990</v>
+        <v>219955</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sågaretorpet-Segskinnet, Sågaretorpet, Sm</t>
+          <t>Dädesjö-Linnebjörke 900 m SO, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508521</v>
+        <v>509099</v>
       </c>
       <c r="R13" t="n">
-        <v>6312746</v>
+        <v>6316090</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2017-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2017-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,26 +2045,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Lisa Petersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Lisa Petersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>78730793</v>
+        <v>108731310</v>
       </c>
       <c r="B14" t="n">
-        <v>58114</v>
+        <v>57794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,41 +2077,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102621</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sågaretorpet-Segskinnet, Sågaretorpet, Sm</t>
+          <t>Sågaretorpet, Sågaretorpet, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508521</v>
+        <v>508548</v>
       </c>
       <c r="R14" t="n">
-        <v>6312746</v>
+        <v>6312964</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2130,12 +2143,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>04:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>04:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>78730754</v>
+        <v>78730798</v>
       </c>
       <c r="B15" t="n">
-        <v>43219</v>
+        <v>58497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,36 +2196,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>201028</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2254,7 +2276,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2273,45 +2294,36 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>78730767</v>
+        <v>78730793</v>
       </c>
       <c r="B16" t="n">
-        <v>43378</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>201075</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2365,7 +2377,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2384,50 +2395,47 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116144793</v>
+        <v>78730754</v>
       </c>
       <c r="B17" t="n">
-        <v>104628</v>
+        <v>43219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>201028</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2465,12 +2473,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,48 +2506,61 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7508</v>
+        <v>78730767</v>
       </c>
       <c r="B18" t="n">
-        <v>56766</v>
+        <v>43378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100077</v>
+        <v>201075</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ossmaden, Sm</t>
+          <t>Sågaretorpet-Segskinnet, Sågaretorpet, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509194</v>
+        <v>508521</v>
       </c>
       <c r="R18" t="n">
-        <v>6312808</v>
+        <v>6312746</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,12 +2584,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2009-03-31</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2009-03-31</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,50 +2598,51 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mia Bisther</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mia Bisther</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>82515894</v>
+        <v>116144793</v>
       </c>
       <c r="B19" t="n">
-        <v>58114</v>
+        <v>104628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2628,24 +2650,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Osmaden, Sågaretorpet, Sm</t>
+          <t>Sågaretorpet-Segskinnet, Sågaretorpet, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509218</v>
+        <v>508521</v>
       </c>
       <c r="R19" t="n">
-        <v>6312793</v>
+        <v>6312746</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,12 +2698,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-02-29</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-02-29</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,6 +2712,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2697,66 +2724,55 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist, Johannes Rydström</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104510627</v>
+        <v>7508</v>
       </c>
       <c r="B20" t="n">
-        <v>93235</v>
+        <v>56766</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>100077</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnvägen, Kvarnvägen, Kattafly, Sm</t>
+          <t>Ossmaden, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508240</v>
+        <v>509194</v>
       </c>
       <c r="R20" t="n">
-        <v>6311562</v>
+        <v>6312808</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2780,12 +2796,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
+          <t>2009-03-31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
+          <t>2009-03-31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2794,26 +2810,25 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Mia Bisther</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Mia Bisther</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122666650</v>
+        <v>82515894</v>
       </c>
       <c r="B21" t="n">
         <v>58114</v>
@@ -2843,7 +2858,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2856,14 +2871,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnvägen, Kvarnvägen, Kattafly, Sm</t>
+          <t>Osmaden, Sågaretorpet, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508240</v>
+        <v>509218</v>
       </c>
       <c r="R21" t="n">
-        <v>6311562</v>
+        <v>6312793</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,22 +2905,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>07:15</t>
+          <t>2020-02-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>07:15</t>
+          <t>2020-02-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,63 +2930,66 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Tomas Lundqvist, Johannes Rydström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>73290312</v>
+        <v>104510627</v>
       </c>
       <c r="B22" t="n">
-        <v>58327</v>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Linje 3, Herråkra 05F2C (Standardrutt), Sm</t>
+          <t>Kvarnvägen, Kvarnvägen, Kattafly, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510530</v>
+        <v>508240</v>
       </c>
       <c r="R22" t="n">
-        <v>6310941</v>
+        <v>6311562</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3005,22 +3013,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>05:45</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>06:15</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3029,74 +3027,79 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>73290284</v>
+        <v>122666650</v>
       </c>
       <c r="B23" t="n">
-        <v>58439</v>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Linje 3, Herråkra 05F2C (Standardrutt), Sm</t>
+          <t>Kvarnvägen, Kvarnvägen, Kattafly, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510530</v>
+        <v>508240</v>
       </c>
       <c r="R23" t="n">
-        <v>6310941</v>
+        <v>6311562</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3120,22 +3123,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,22 +3153,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>73290329</v>
+        <v>73290312</v>
       </c>
       <c r="B24" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3173,16 +3176,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3192,7 +3195,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -3277,10 +3280,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>73290331</v>
+        <v>73290284</v>
       </c>
       <c r="B25" t="n">
-        <v>58085</v>
+        <v>58439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3288,26 +3291,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205976</v>
+        <v>103018</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3392,10 +3395,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124350795</v>
+        <v>73290329</v>
       </c>
       <c r="B26" t="n">
-        <v>57141</v>
+        <v>58636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,46 +3406,45 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Magersryd, Sm</t>
+          <t>Linje 3, Herråkra 05F2C (Standardrutt), Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507952</v>
+        <v>510530</v>
       </c>
       <c r="R26" t="n">
-        <v>6310311</v>
+        <v>6310941</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3466,22 +3468,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3496,39 +3498,39 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ellen Flygare</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ellen Flygare</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>100448862</v>
+        <v>73290331</v>
       </c>
       <c r="B27" t="n">
-        <v>56522</v>
+        <v>58085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>205976</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3538,31 +3540,23 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vägen Herråkra - Attsjö, Sm</t>
+          <t>Linje 3, Herråkra 05F2C (Standardrutt), Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507993</v>
+        <v>510530</v>
       </c>
       <c r="R27" t="n">
-        <v>6310259</v>
+        <v>6310941</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3589,22 +3583,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,15 +3613,254 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124350795</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Magersryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>507952</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6310311</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dädesjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ellen Flygare</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ellen Flygare</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>100448862</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vägen Herråkra - Attsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>507993</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6310259</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dädesjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Love Eriksen</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Love Eriksen</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 649-2023 artfynd.xlsx
+++ b/artfynd/S 649-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66343219</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121245134</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74602272</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74604745</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134608591</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134736762</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134608641</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1575,6 +1615,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134735543</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,6 +1743,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134608642</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1826,6 +1876,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134735544</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1946,6 +2001,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127902690</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2063,6 +2123,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66343246</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2182,6 +2247,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108731310</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2291,6 +2361,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78730798</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2392,6 +2467,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78730793</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2503,6 +2583,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78730754</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2614,6 +2699,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78730767</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2728,6 +2818,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116144793</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2825,6 +2920,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7508</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2934,6 +3034,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82515894</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3043,6 +3148,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104510627</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3162,6 +3272,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122666650</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3277,6 +3392,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73290312</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3392,6 +3512,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73290284</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3507,6 +3632,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73290329</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3622,6 +3752,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73290331</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3738,6 +3873,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124350795</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3861,8 +4001,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100448862</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>